--- a/data/trans_orig/IP07C13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C13-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54799</t>
+          <t>54453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71068</t>
+          <t>71506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59204</t>
+          <t>58802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77030</t>
+          <t>77152</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118005</t>
+          <t>118600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142745</t>
+          <t>142389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35196</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51640</t>
+          <t>51340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40777</t>
+          <t>40788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58179</t>
+          <t>58789</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80630</t>
+          <t>81344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105202</t>
+          <t>105311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13207</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73818</t>
+          <t>75156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95751</t>
+          <t>95892</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>97306</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118441</t>
+          <t>117875</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>177951</t>
+          <t>178171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207858</t>
+          <t>207937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64815</t>
+          <t>65075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87256</t>
+          <t>85986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53059</t>
+          <t>53320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73353</t>
+          <t>73530</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123915</t>
+          <t>123455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153273</t>
+          <t>153034</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>457</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7099</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133529</t>
+          <t>134832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161198</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161906</t>
+          <t>162688</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189519</t>
+          <t>190414</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>304489</t>
+          <t>303698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>342651</t>
+          <t>342868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>103672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131644</t>
+          <t>132260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99791</t>
+          <t>99166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126102</t>
+          <t>125817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213939</t>
+          <t>212815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251174</t>
+          <t>250509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>21170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26225</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45076</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,82 +2450,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>4460</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>8847</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4137</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>4460</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>9023</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83266</t>
+          <t>83080</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>102296</t>
+          <t>102858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90970</t>
+          <t>90103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111053</t>
+          <t>110325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>179073</t>
+          <t>179134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207382</t>
+          <t>208614</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37779</t>
+          <t>37781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56029</t>
+          <t>56180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34152</t>
+          <t>35490</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53221</t>
+          <t>55779</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76668</t>
+          <t>76320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105268</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10292</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7713</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76747</t>
+          <t>76893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97737</t>
+          <t>98360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96067</t>
+          <t>96790</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117133</t>
+          <t>117101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>181205</t>
+          <t>180388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209506</t>
+          <t>209433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46353</t>
+          <t>46495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66738</t>
+          <t>66107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44605</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64518</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97774</t>
+          <t>96997</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124320</t>
+          <t>125883</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>21282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>26012</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166825</t>
+          <t>165546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195940</t>
+          <t>194972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>194093</t>
+          <t>192686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>223353</t>
+          <t>220965</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>367535</t>
+          <t>369661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>410143</t>
+          <t>410537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>89774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117377</t>
+          <t>116250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83841</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>111232</t>
+          <t>112198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179967</t>
+          <t>178860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>219754</t>
+          <t>218754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>20327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25944</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45508</t>
+          <t>45731</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de estar contento con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99564</t>
+          <t>99445</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120425</t>
+          <t>121841</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99284</t>
+          <t>98784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119920</t>
+          <t>121271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205254</t>
+          <t>206059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236392</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46410</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65780</t>
+          <t>66849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,82 +5412,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>25,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>50614</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41583</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>61323</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>28,54%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>23,44%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>34,57%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>106397</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>92241</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>121189</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>29,8%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>25,84%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>50614</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>41090</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60873</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>34,32%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>106397</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>91838</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>120257</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>29,8%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>25,73%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>19663</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31593</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72385</t>
+          <t>72113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93085</t>
+          <t>93211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87572</t>
+          <t>87199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108959</t>
+          <t>108864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164802</t>
+          <t>165203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196264</t>
+          <t>194984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56806</t>
+          <t>56319</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76581</t>
+          <t>77731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53876</t>
+          <t>53980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75212</t>
+          <t>74999</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116046</t>
+          <t>116334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146764</t>
+          <t>146368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14343</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14056</t>
+          <t>13445</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28382</t>
+          <t>27908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>178355</t>
+          <t>178210</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>208211</t>
+          <t>208269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192947</t>
+          <t>193436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>223949</t>
+          <t>225122</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380049</t>
+          <t>380194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>422422</t>
+          <t>424561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,32%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107989</t>
+          <t>108685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136174</t>
+          <t>137970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99605</t>
+          <t>101107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129345</t>
+          <t>130178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217171</t>
+          <t>217140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259697</t>
+          <t>260226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15114</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30508</t>
+          <t>30497</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32642</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>53247</t>
+          <t>54780</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8823</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C13-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C13-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser, percibida por el/la menor [KIDSCREEN 20] en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>67771</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>59250</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>76336</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>48,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>62826</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>54453</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71506</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>54880</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>71530</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>56,24%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>64,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>67771</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>58802</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>77152</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118600</t>
+          <t>117794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142389</t>
+          <t>142085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49866</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41112</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>58207</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43034</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>34769</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51340</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>34955</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51060</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>49866</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>40788</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>58789</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81344</t>
+          <t>81015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105311</t>
+          <t>105642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3939</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8004</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4464</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1892</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8122</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9334</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3939</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1879</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8003</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3493</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1387</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5037</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4864</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2926</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>575</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122154</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122154</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122154</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122154</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>122154</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>122154</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>108333</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>97969</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>119312</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>84994</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>75156</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95892</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>74398</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>97177</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>47,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>108333</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>97306</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>117875</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178171</t>
+          <t>179038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207937</t>
+          <t>207578</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>63084</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52540</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73622</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>75394</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65075</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85986</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64083</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85593</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>42,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,05%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63084</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>53320</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>73530</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>123455</t>
+          <t>124087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153034</t>
+          <t>154568</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10551</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6364</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16258</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15308</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9997</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>22201</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9697</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21362</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,56%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10551</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6249</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>16480</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34701</t>
+          <t>34055</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3839</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1828</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4982</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3371</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5428</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4954</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4992</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4800</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184640</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184640</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184640</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184640</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184640</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>176103</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>161663</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>189215</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>57,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>61,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>147819</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>134832</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>163562</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>133919</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>161721</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>50,86%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,39%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>176103</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>162688</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>190414</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>303698</t>
+          <t>302383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>342868</t>
+          <t>343181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>112950</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>99150</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127182</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>118428</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>103672</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>132260</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>104321</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>131106</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>40,75%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>112950</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>99166</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>125817</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>212815</t>
+          <t>213990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>250509</t>
+          <t>252232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14489</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9297</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>21873</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,13%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19772</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14120</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>27814</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13301</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>27071</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,8%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>14489</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>9595</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>21170</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43856</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4402</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3215</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7252</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7127</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4386</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6657</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1412</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4811</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5033</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5355</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>306794</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>306794</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>306794</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>306794</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>306794</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>306794</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser, percibida por el/la menor [KIDSCREEN 20] en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>100752</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>90471</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>110179</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>64,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>93022</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>83080</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>102858</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>83094</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>102957</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>62,03%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>100752</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>90103</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>110325</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>64,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>179134</t>
+          <t>179710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208614</t>
+          <t>208343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44154</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35386</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53523</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>46396</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>37781</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56180</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>37172</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>56322</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>30,94%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,46%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>44154</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>35490</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>55779</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76320</t>
+          <t>77815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103771</t>
+          <t>103549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8530</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4713</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14187</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7170</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3771</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3404</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13082</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8530</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4357</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14615</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>22389</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3273</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1278</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4428</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4249</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2099</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6267</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5722</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1384</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4331</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>107358</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>95858</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>117457</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>87752</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>76893</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>98360</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>77873</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98905</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>107358</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>96790</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>117101</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>63,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180388</t>
+          <t>181048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>209433</t>
+          <t>209797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53809</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>44319</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>64278</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>37,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>56456</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>66107</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>46755</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>66724</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>34,95%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>53809</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>44299</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>64044</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96997</t>
+          <t>96359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125883</t>
+          <t>124692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,61%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4868</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2193</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9170</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>14351</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8901</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21282</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9137</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21350</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,88%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>4868</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>8738</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26012</t>
+          <t>26956</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -4019,107 +4019,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2532</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6327</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>697</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5136</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3478</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2532</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6385</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7077</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3229</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>7177</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5485</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2296</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6345</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6474</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1458</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5700</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170026</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170026</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170026</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>161553</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>161553</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>161553</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170026</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170026</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>208111</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>193595</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>221920</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>180775</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>165546</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>194972</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>165751</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>195983</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>58,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>208111</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>192686</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>220965</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>369661</t>
+          <t>369169</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>410537</t>
+          <t>409086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>97963</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>84817</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>112308</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,1%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>102852</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>89774</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>116250</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>89268</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>117049</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,02%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,82%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>97963</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>85188</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>112198</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178860</t>
+          <t>181291</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>218754</t>
+          <t>219027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -4588,107 +4588,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13398</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8520</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>20363</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>21521</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>15437</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>31250</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14966</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>29351</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,91%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>13398</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>8314</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>20327</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>9,42%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>34919</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>26264</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>46068</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>4,12%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>34919</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>26844</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>45731</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3139</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1975</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5318</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3139</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7561</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2842</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7436</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>4395</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8979</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1612</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8643</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>728</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6816</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12799</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>325454</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>325454</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>325454</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>311518</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>311518</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>311518</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>325454</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>325454</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>325454</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de estar contento/a con su forma de ser en 2016 (tasa de respuesta: 95,37%)</t>
+          <t>Menores según la frecuencia de estar contento/a con su forma de ser, percibida por el/la menor [KIDSCREEN 20] en 2016 (tasa de respuesta: 95,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>109952</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>98622</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>120377</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>55,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>67,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>110789</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>99445</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>121841</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>99621</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>121698</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,68%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>109952</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>98784</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>121271</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>61,99%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206059</t>
+          <t>206185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235585</t>
+          <t>236747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,32%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41300</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61829</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55783</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46122</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>66849</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>46500</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67061</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,22%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>50614</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>41583</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61323</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92241</t>
+          <t>91394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121189</t>
+          <t>120255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12842</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8214</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19889</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>10232</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5593</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16599</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16855</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12842</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7542</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19663</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15933</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>31023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7678</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1666</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5737</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5845</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3234</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7663</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3612</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1147</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4024</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3688</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>177369</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>177369</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>177369</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>179617</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>179617</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>179617</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>177369</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>177369</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>177369</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>98278</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86997</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>108337</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>57,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>82484</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72113</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>93211</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>71620</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>92789</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>50,05%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>98278</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>87199</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>108864</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>57,61%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165203</t>
+          <t>164438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194984</t>
+          <t>194715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,05%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64045</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54116</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74450</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66817</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>56319</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77731</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57133</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78986</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,54%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>64045</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>53980</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74999</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116334</t>
+          <t>116032</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146368</t>
+          <t>145782</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8269</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13855</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11458</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6567</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17892</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7038</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>18764</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,95%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8269</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4222</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13851</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13445</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>28284</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1874</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5354</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5314</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2175</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6269</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,74 +6638,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>208229</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>191044</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>222047</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>59,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,9%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>63,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>193274</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>178210</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>208269</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>176960</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>208271</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>56,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51,74%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>51,38%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>60,47%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>208229</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>193436</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>225122</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>59,84%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>55,59%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>64,7%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>558</t>
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380194</t>
+          <t>379239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424561</t>
+          <t>422409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>114659</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>101010</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>130419</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>32,95%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>122600</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>108685</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>137970</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>107494</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>137595</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,06%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>114659</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>101107</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>130178</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>32,95%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217140</t>
+          <t>216529</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260226</t>
+          <t>258275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>21111</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14789</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29470</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>21689</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14856</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>30497</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>15206</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>29343</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,3%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>21111</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>14495</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>29382</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33016</t>
+          <t>32763</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54780</t>
+          <t>54245</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8401</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3540</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7640</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8201</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3234</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>797</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7919</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3998</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>3322</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7690</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7599</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4077</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>347960</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>347960</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>347960</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>491</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>344425</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>344425</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>344425</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>347960</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>347960</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>347960</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
